--- a/output/pdf_financials_xlsx/VNP.xlsx
+++ b/output/pdf_financials_xlsx/VNP.xlsx
@@ -1895,10 +1895,10 @@
         <v>34.706</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>22.142</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>59.573</v>
       </c>
     </row>
     <row r="35">
@@ -1985,10 +1985,10 @@
         <v>34.706</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>22.142</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>59.573</v>
       </c>
     </row>
     <row r="37">
@@ -5945,16 +5945,16 @@
         </is>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-5</v>
+        <v>-7.999</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-12.5</v>
+        <v>-15.358</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-10</v>
+        <v>-13.052</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-15.144</v>
+        <v>-18.309</v>
       </c>
     </row>
     <row r="125">
@@ -5990,16 +5990,16 @@
         </is>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-5</v>
+        <v>-7.999</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-12.5</v>
+        <v>-15.358</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-10</v>
+        <v>-13.052</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-15.144</v>
+        <v>-18.309</v>
       </c>
     </row>
     <row r="126">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22700,7 +22700,11 @@
           <t>Principal elements of lease payments 20</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -25538,7 +25542,11 @@
           <t>Principal elements of lease payments 21</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -38058,7 +38066,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -39688,7 +39696,7 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -45646,7 +45654,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
@@ -51074,7 +51082,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -51792,7 +51800,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -55078,7 +55086,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>OtherInterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E646" s="5" t="n">

--- a/output/pdf_financials_xlsx/VNP.xlsx
+++ b/output/pdf_financials_xlsx/VNP.xlsx
@@ -1637,31 +1637,31 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>10.686</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>11.148</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>27.166</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>10.739</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>8.81</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>9.669</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>12.535</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.313</v>
+        <v>17.732</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>16.11</v>
@@ -1670,7 +1670,7 @@
         <v>16.791</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>2.845</v>
+        <v>17.369</v>
       </c>
     </row>
     <row r="29">
@@ -1680,31 +1680,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>44.693</v>
+        <v>55.379</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>19.527</v>
+        <v>30.675</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-90.82899999999999</v>
+        <v>-63.663</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.869</v>
+        <v>6.87</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.54</v>
+        <v>20.766</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>13.916</v>
+        <v>22.726</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.833</v>
+        <v>13.502</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>28.239</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-14.975</v>
+        <v>-0.556</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>38.323</v>
@@ -1713,7 +1713,7 @@
         <v>53.332</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>68.55</v>
+        <v>83.074</v>
       </c>
     </row>
     <row r="30">
@@ -1723,31 +1723,31 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>9.736782480632316</v>
+        <v>12.06482619190784</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3.842422692076861</v>
+        <v>6.036068831846044</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-29.20433938240325</v>
+        <v>-20.46962818154926</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1.671288736835739</v>
+        <v>2.967628230049504</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5.702177194928973</v>
+        <v>9.442696302224487</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>6.383632652125049</v>
+        <v>10.42500974793</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.955901638507739</v>
+        <v>6.88979491863592</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.44778322777275</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-5.667561113150634</v>
+        <v>-0.2104283124481972</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>15.811710146841</v>
@@ -1756,7 +1756,7 @@
         <v>18.43605352581054</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>17.52918974484864</v>
+        <v>21.24317883097821</v>
       </c>
     </row>
     <row r="31">
@@ -4839,25 +4839,25 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>10.686</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>11.148</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>27.166</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>10.739</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>8.226000000000001</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>8.81</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>9.669</v>
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
@@ -4865,16 +4865,16 @@
         </is>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>17.732</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>16.11</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>16.791</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>17.369</v>
       </c>
     </row>
     <row r="101">
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.245</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2.174</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -5391,13 +5391,13 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>3.987</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
@@ -5405,16 +5405,16 @@
         </is>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>4.205</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="113">
@@ -20684,7 +20684,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -20758,7 +20762,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -20834,7 +20842,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -22032,7 +22040,11 @@
           <t>Additions of intangible assets 9</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -22258,7 +22270,11 @@
           <t>Proceeds on disposal of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -23354,7 +23370,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -23428,7 +23448,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -23504,7 +23528,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -24936,7 +24960,11 @@
           <t>Additions of intangible assets 10</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -25238,7 +25266,11 @@
           <t>Proceeds on disposal of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -25980,7 +26012,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -27172,7 +27208,11 @@
           <t>Additions of intangible assets 8</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -27242,7 +27282,11 @@
           <t>Proceeds on disposal of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -28898,7 +28942,11 @@
           <t>Additions of intangible assets 7</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -29506,7 +29554,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -31162,7 +31214,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -34558,7 +34614,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E373" s="5" t="n">
         <v>0.245</v>
       </c>
@@ -35680,7 +35740,11 @@
           <t>Depreciation of property, plant and equipment and amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E388" s="5" t="n">
         <v>10.686</v>
       </c>
@@ -37116,7 +37180,11 @@
           <t>Additions of intangible assets (Note 8)</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E407" s="5" t="n">
         <v>-0.797</v>
       </c>

--- a/output/pdf_financials_xlsx/VNP.xlsx
+++ b/output/pdf_financials_xlsx/VNP.xlsx
@@ -1117,7 +1117,7 @@
         <v>-2.048</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.63</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-4.711</v>
@@ -2018,10 +2018,8 @@
       <c r="H37" s="3" t="n">
         <v>28.477</v>
       </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="3" t="n">
+        <v>34.865</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>32.872</v>
@@ -2142,33 +2140,31 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.187</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.988</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.743</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.499</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>3.725</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>3.504</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>3.357</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>2.908</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>1.827</v>
       </c>
     </row>
     <row r="41">
@@ -2187,16 +2183,16 @@
         <v>37.325</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>29.799</v>
+        <v>30.986</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>25.639</v>
+        <v>26.627</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>22.984</v>
+        <v>23.727</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>28.477</v>
+        <v>28.976</v>
       </c>
       <c r="I41" s="1" t="inlineStr">
         <is>
@@ -2204,16 +2200,16 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>32.872</v>
+        <v>36.376</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>33.437</v>
+        <v>36.794</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>42.172</v>
+        <v>45.08</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>50.47</v>
+        <v>52.297</v>
       </c>
     </row>
     <row r="42">
@@ -2881,27 +2877,25 @@
         <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>99.066</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>90.79300000000001</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0</v>
+        <v>84.337</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>89.393</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>97.86799999999999</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>135.249</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0</v>
+        <v>140.301</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>0</v>
@@ -2926,27 +2920,25 @@
         <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>31.42</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>30.848</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0</v>
+        <v>27.73</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0</v>
+        <v>32.096</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>39.278</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>53.723</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0</v>
+        <v>62.35</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>0</v>
@@ -5154,25 +5146,25 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.668</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>2.246</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>3.422</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>1.334</v>
       </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
@@ -5180,16 +5172,16 @@
         </is>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>1.893</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>2.768</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>7.189</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>17.322</v>
       </c>
     </row>
     <row r="108">
@@ -21214,7 +21206,11 @@
           <t>Share-based compensation expense 23</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -23902,7 +23898,11 @@
           <t>Share-based compensation expense 24</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -26236,7 +26236,11 @@
           <t>Share‐based compensation expense 21</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -28116,7 +28120,11 @@
           <t>Share‐based compensation expense 21</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -29702,7 +29710,11 @@
           <t>Share‐based compensation expense 21</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -31518,7 +31530,11 @@
           <t>Share‐based compensation expense 21</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -33482,7 +33498,11 @@
           <t>Share-based compensation expense 22</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -35968,7 +35988,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E391" s="5" t="n">
         <v>0.5669999999999999</v>
       </c>
@@ -41542,7 +41566,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -45800,7 +45828,11 @@
           <t>Income taxes (recovery) expense (292) 1,314 4,711</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
